--- a/Outputs/Recycling_Plot_Data/Repeal/06_Needed_Recycling_Capacity_data_Repeal.xlsx
+++ b/Outputs/Recycling_Plot_Data/Repeal/06_Needed_Recycling_Capacity_data_Repeal.xlsx
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="F26">
-        <v>0.06386637622506218</v>
+        <v>0.05189806886616198</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="F28">
-        <v>0.3538546366463742</v>
+        <v>0.3065875442859745</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="F30">
-        <v>0.8288707458044084</v>
+        <v>0.740545153131859</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="F32">
-        <v>1.49011002755455</v>
+        <v>1.35887337655005</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="F33">
-        <v>0.1767457621971418</v>
+        <v>0.1338347038651914</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="F34">
-        <v>2.337830735009423</v>
+        <v>2.166829739691893</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="F35">
-        <v>0.5399729500990147</v>
+        <v>0.4572975474540346</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="F36">
-        <v>3.381010221664578</v>
+        <v>3.177371670999351</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F37">
-        <v>1.098658917201169</v>
+        <v>0.9833459592084913</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         </is>
       </c>
       <c r="F38">
-        <v>4.634802003563209</v>
+        <v>4.406940364585712</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="F39">
-        <v>1.8679571795468</v>
+        <v>1.728421133241854</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="F40">
-        <v>6.120401142492602</v>
+        <v>5.875601427781746</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="F41">
-        <v>2.869062798923193</v>
+        <v>2.712588676884887</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="F42">
-        <v>7.859015581982084</v>
+        <v>7.602381371681553</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="F43">
-        <v>4.123183718859676</v>
+        <v>3.954875101231694</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         </is>
       </c>
       <c r="F44">
-        <v>9.874130399693634</v>
+        <v>9.608797341624921</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="F45">
-        <v>5.653805017018226</v>
+        <v>5.476797551622061</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         </is>
       </c>
       <c r="F46">
-        <v>12.17055518495982</v>
+        <v>11.89834862685045</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="F47">
-        <v>7.46573628273141</v>
+        <v>7.281855317294587</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         </is>
       </c>
       <c r="F48">
-        <v>14.74432849335426</v>
+        <v>14.46626022701734</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="F49">
-        <v>9.555016071572847</v>
+        <v>9.36527339790848</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="F50">
-        <v>17.58492523936959</v>
+        <v>17.30143381575065</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="F51">
-        <v>11.91111929803518</v>
+        <v>11.71595346708879</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="F52">
-        <v>20.67738601962959</v>
+        <v>20.38854119065434</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="F53">
-        <v>14.51908655874217</v>
+        <v>14.31856732243948</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="F78">
-        <v>0.06714721845479717</v>
+        <v>0.05517448898134276</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         </is>
       </c>
       <c r="F80">
-        <v>0.362146911888222</v>
+        <v>0.3148711449301635</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3056,7 +3056,7 @@
         </is>
       </c>
       <c r="F82">
-        <v>0.8450231877141716</v>
+        <v>0.7566812403317685</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="F84">
-        <v>1.518643330564798</v>
+        <v>1.38737706992291</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="F85">
-        <v>0.1891266232976266</v>
+        <v>0.1462023100381414</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="F86">
-        <v>2.385286670475548</v>
+        <v>2.21423603188086</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         </is>
       </c>
       <c r="F87">
-        <v>0.5712764436553766</v>
+        <v>0.4885677524430916</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="F88">
-        <v>3.456189625348823</v>
+        <v>3.252474471076101</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="F89">
-        <v>1.157685878975651</v>
+        <v>1.042312672085333</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="F90">
-        <v>4.748794686639037</v>
+        <v>4.52082180669086</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="F91">
-        <v>1.965797420712865</v>
+        <v>1.826166488147091</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="F92">
-        <v>6.28637977278709</v>
+        <v>6.041426770080393</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         </is>
       </c>
       <c r="F93">
-        <v>3.018888987307918</v>
+        <v>2.862277931983625</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="F94">
-        <v>8.092174938752041</v>
+        <v>7.835336347815155</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="F95">
-        <v>4.34019063371987</v>
+        <v>4.171693990165386</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F96">
-        <v>10.19200655047625</v>
+        <v>9.926404338220502</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         </is>
       </c>
       <c r="F97">
-        <v>5.95552872589108</v>
+        <v>5.778268461017731</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="F98">
-        <v>12.59239505474362</v>
+        <v>12.31983418225901</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         </is>
       </c>
       <c r="F99">
-        <v>7.871423710605445</v>
+        <v>7.687204785503242</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="F100">
-        <v>15.29064743672144</v>
+        <v>15.01210972773193</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="F101">
-        <v>10.08518257303027</v>
+        <v>9.894986811423161</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="F102">
-        <v>18.27683165787534</v>
+        <v>17.99271390356459</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="F103">
-        <v>12.58687327463117</v>
+        <v>12.39109746770282</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="F104">
-        <v>21.5358906982815</v>
+        <v>21.24621390711071</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         </is>
       </c>
       <c r="F105">
-        <v>15.36143879548432</v>
+        <v>15.16010395169594</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         </is>
       </c>
       <c r="F128">
-        <v>0.1204371547219402</v>
+        <v>0.1112984771157621</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="F130">
-        <v>0.4298940412077882</v>
+        <v>0.4080777205510692</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         </is>
       </c>
       <c r="F132">
-        <v>1.01265544060375</v>
+        <v>0.954698246531835</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         </is>
       </c>
       <c r="F133">
-        <v>0.09826787984296191</v>
+        <v>0.06212700642776559</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="F134">
-        <v>1.837460428688514</v>
+        <v>1.73742327248465</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="F135">
-        <v>0.4385793483747258</v>
+        <v>0.3603585128275808</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="F136">
-        <v>2.92412464632372</v>
+        <v>2.780039223757407</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="F137">
-        <v>1.040750046456932</v>
+        <v>0.9184809445473371</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4904,7 +4904,7 @@
         </is>
       </c>
       <c r="F138">
-        <v>4.293042837871679</v>
+        <v>4.10803946997914</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         </is>
       </c>
       <c r="F139">
-        <v>1.92517471845189</v>
+        <v>1.76198767121607</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="F140">
-        <v>5.976311591106788</v>
+        <v>5.757587092887181</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="F141">
-        <v>3.123949952134</v>
+        <v>2.927041774571111</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         </is>
       </c>
       <c r="F142">
-        <v>8.01600669650397</v>
+        <v>7.772074616539009</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
         </is>
       </c>
       <c r="F143">
-        <v>4.679151537978181</v>
+        <v>4.457035778669939</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="F144">
-        <v>10.46174253591515</v>
+        <v>10.19996952823981</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="F145">
-        <v>6.640393857836358</v>
+        <v>6.400437170817741</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="F146">
-        <v>13.36465673496851</v>
+        <v>13.09016355253845</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="F147">
-        <v>9.058814537336721</v>
+        <v>8.806137675563386</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         </is>
       </c>
       <c r="F148">
-        <v>16.78228341741513</v>
+        <v>16.49812643341632</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="F149">
-        <v>11.99194770023034</v>
+        <v>11.72960703688825</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
         </is>
       </c>
       <c r="F150">
-        <v>20.74660628083083</v>
+        <v>20.4544240299533</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         </is>
       </c>
       <c r="F151">
-        <v>15.47177704409304</v>
+        <v>15.20141111387223</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="F152">
-        <v>25.27505658844635</v>
+        <v>24.97554125599944</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -5399,7 +5399,7 @@
         </is>
       </c>
       <c r="F153">
-        <v>19.51573383215556</v>
+        <v>19.23803482036536</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="F154">
-        <v>30.36065706351335</v>
+        <v>30.05378392219243</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="F155">
-        <v>24.11684078766957</v>
+        <v>23.83178396700536</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         </is>
       </c>
       <c r="F156">
-        <v>35.98224469350875</v>
+        <v>35.66753680061994</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         </is>
       </c>
       <c r="F157">
-        <v>29.25393489811195</v>
+        <v>28.96104332587987</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="F180">
-        <v>0.1233115576888181</v>
+        <v>0.114169988677189</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="F182">
-        <v>0.4373267657085521</v>
+        <v>0.415499198504754</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="F184">
-        <v>1.027129851812395</v>
+        <v>0.9691515202028977</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="F185">
-        <v>0.1053095665508427</v>
+        <v>0.06915880214514362</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -6488,7 +6488,7 @@
         </is>
       </c>
       <c r="F186">
-        <v>1.8629950822456</v>
+        <v>1.762920856459435</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="F187">
-        <v>0.4566812774310475</v>
+        <v>0.3784346188486811</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="F188">
-        <v>2.967077079657137</v>
+        <v>2.822929368256904</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         </is>
       </c>
       <c r="F189">
-        <v>1.076269755289584</v>
+        <v>0.9539496110931501</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="F190">
-        <v>4.362765640649455</v>
+        <v>4.177664013330583</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="F191">
-        <v>1.987464796728902</v>
+        <v>1.824190736613828</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="F192">
-        <v>6.085733774662875</v>
+        <v>5.86686434679375</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="F193">
-        <v>3.225939411189322</v>
+        <v>3.028897550523995</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         </is>
       </c>
       <c r="F194">
-        <v>8.182008821463816</v>
+        <v>7.937873360729249</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="F195">
-        <v>4.837720938437262</v>
+        <v>4.615413044906495</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="F196">
-        <v>10.70522403887722</v>
+        <v>10.44317763111334</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         </is>
       </c>
       <c r="F197">
-        <v>6.876442636297661</v>
+        <v>6.636223795737588</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         </is>
       </c>
       <c r="F198">
-        <v>13.71079322445858</v>
+        <v>13.43594179169098</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         </is>
       </c>
       <c r="F199">
-        <v>9.397518302326022</v>
+        <v>9.144494436762221</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="F200">
-        <v>17.26135948349665</v>
+        <v>16.97673604515018</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="F201">
-        <v>12.4635910418111</v>
+        <v>12.20079517066842</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         </is>
       </c>
       <c r="F202">
-        <v>21.39328529664035</v>
+        <v>21.10049270613942</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         </is>
       </c>
       <c r="F203">
-        <v>16.1110233354018</v>
+        <v>15.84005831210466</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         </is>
       </c>
       <c r="F204">
-        <v>26.12780475499358</v>
+        <v>25.82748156976161</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         </is>
       </c>
       <c r="F205">
-        <v>20.36104927420202</v>
+        <v>20.08255365617385</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="F206">
-        <v>31.45994506011104</v>
+        <v>31.15199161614399</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         </is>
       </c>
       <c r="F207">
-        <v>25.20869605976648</v>
+        <v>24.92257018300323</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         </is>
       </c>
       <c r="F208">
-        <v>37.36905268771553</v>
+        <v>37.05290392328236</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         </is>
       </c>
       <c r="F209">
-        <v>30.63331016781798</v>
+        <v>30.33898897058859</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
